--- a/questionnaire_templates/033_female_archetype_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/033_female_archetype_assessment--questionnaire_templates.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +43,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,9 +64,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -430,9 +440,9 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -510,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_1</t>
+          <t>female_archetype_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>What is your age?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -528,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_2</t>
+          <t>female_archetype_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you agree</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -551,115 +561,115 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_3</t>
+          <t>female_archetype_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>What is your relationship status?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_4</t>
+          <t>female_archetype_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>What is your highest level of education completed?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_5</t>
+          <t>female_archetype_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>How often do you exercise?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_6</t>
+          <t>female_archetype_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>How do you rate your overall health?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_7</t>
+          <t>female_archetype_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>How do you rate your mental health?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -671,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_8</t>
+          <t>female_archetype_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>What is your current job title or position?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -694,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_9</t>
+          <t>female_archetype_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>What is your annual income range?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -717,41 +727,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_10</t>
+          <t>female_archetype_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>What is your current residence?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_11</t>
+          <t>female_archetype_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you live with any family members?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -763,18 +773,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_12</t>
+          <t>female_archetype_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>How many people live in your household?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -786,18 +796,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_13</t>
+          <t>female_archetype_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>What is your occupation?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -809,271 +819,271 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_14</t>
+          <t>female_archetype_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>How many dependents do you have?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_15</t>
+          <t>female_archetype_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any chronic medical conditions?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_16</t>
+          <t>female_archetype_16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any disabilities or impairments?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_17</t>
+          <t>female_archetype_17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any allergies or sensitivities?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_18</t>
+          <t>female_archetype_18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any chronic pain or discomfort?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_19</t>
+          <t>female_archetype_19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any medical insurance?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_20</t>
+          <t>female_archetype_20</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any mental health issues?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_21</t>
+          <t>female_archetype_21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>How much stress do you experience in your daily life?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_22</t>
+          <t>female_archetype_22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any financial difficulties?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_23</t>
+          <t>female_archetype_23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any substance abuse issues?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_24</t>
+          <t>female_archetype_24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any housing difficulties?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>female_archetype_assessment_form_25</t>
+          <t>female_archetype_25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Female Archetype Assessment Form</t>
+          <t>Do you have any other health issues?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1083,6 +1093,926 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>list_name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>female_archetype_2_choices</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>i_agree</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>I agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>female_archetype_2_choices</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>i_do_not_agree</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>I do not agree</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>female_archetype_3_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Single</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>female_archetype_3_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>in_a_relationship</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>In a relationship</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>female_archetype_3_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>married</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Married</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>female_archetype_3_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>engaged</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Engaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>female_archetype_3_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>widowed</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Widowed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>female_archetype_3_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>divorced</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Divorced</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>female_archetype_4_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>high_school_or_equivalent</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>High school or equivalent</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>female_archetype_4_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>some_college</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Some college</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>female_archetype_4_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>bachelor's_degree</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bachelor's degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>female_archetype_4_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>master's_degree</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Master's degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>female_archetype_4_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>doctoral_degree</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Doctoral degree</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>female_archetype_4_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>female_archetype_5_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>female_archetype_5_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3-4_times_a_week</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3-4 times a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>female_archetype_5_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1-2_times_a_week</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1-2 times a week</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>female_archetype_5_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>female_archetype_6_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>female_archetype_6_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>female_archetype_6_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>female_archetype_6_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>female_archetype_7_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>female_archetype_7_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>female_archetype_7_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>female_archetype_7_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>female_archetype_11_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>female_archetype_11_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>female_archetype_15_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>female_archetype_15_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>female_archetype_16_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>female_archetype_16_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>female_archetype_17_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>female_archetype_17_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>female_archetype_18_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>female_archetype_18_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>female_archetype_19_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>female_archetype_19_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>female_archetype_20_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>female_archetype_20_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>female_archetype_21_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>female_archetype_21_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>some</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Some</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>female_archetype_21_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>a_lot</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>A lot</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>female_archetype_21_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>extreme</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Extreme</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>female_archetype_22_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>female_archetype_22_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>female_archetype_23_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>female_archetype_23_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>female_archetype_24_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>female_archetype_24_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>female_archetype_25_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>female_archetype_25_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
